--- a/SGC-CKN/Excel/346195c8-f4ee-4f00-8dd3-e9f89ac96a0b_Lô_CT-02_P7-68_D800_09-03-2026.xlsx
+++ b/SGC-CKN/Excel/346195c8-f4ee-4f00-8dd3-e9f89ac96a0b_Lô_CT-02_P7-68_D800_09-03-2026.xlsx
@@ -1466,16 +1466,16 @@
         <v>-33.5</v>
       </c>
       <c r="G17" s="25">
-        <v>-35.5</v>
+        <v>-35.54</v>
       </c>
       <c r="H17" s="25">
         <v>1.23</v>
       </c>
       <c r="I17" s="25">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="J17" s="12">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
@@ -1498,7 +1498,7 @@
         <v>58</v>
       </c>
       <c r="F18" s="28">
-        <v>-35.5</v>
+        <v>-35.54</v>
       </c>
       <c r="G18" s="28">
         <v>-36.5</v>
@@ -1507,10 +1507,10 @@
         <v>1.23</v>
       </c>
       <c r="I18" s="28">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="J18" s="31">
-        <v>0.81</v>
+        <v>0.78</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>30</v>
@@ -1912,16 +1912,16 @@
         <v>-33.5</v>
       </c>
       <c r="F8" s="25">
-        <v>-35.5</v>
+        <v>-35.54</v>
       </c>
       <c r="G8" s="25">
         <v>1.23</v>
       </c>
       <c r="H8" s="25">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="I8" s="12">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1938,7 +1938,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-35.5</v>
+        <v>-35.54</v>
       </c>
       <c r="F9" s="28">
         <v>-36.5</v>
@@ -1947,10 +1947,10 @@
         <v>1.23</v>
       </c>
       <c r="H9" s="28">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="I9" s="31">
-        <v>0.81</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
